--- a/samples/ss_krian12_gresik_ingest.xlsx
+++ b/samples/ss_krian12_gresik_ingest.xlsx
@@ -631,31 +631,21 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -702,15 +692,11 @@
       <c r="J3" t="n">
         <v>1</v>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -726,7 +712,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -773,15 +758,11 @@
       <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -797,7 +778,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -826,31 +806,21 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -897,15 +867,11 @@
       <c r="J6" t="n">
         <v>1</v>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -921,7 +887,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -968,15 +933,11 @@
       <c r="J7" t="n">
         <v>1</v>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -992,7 +953,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1021,35 +981,26 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
           <t>seksi A</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1078,31 +1029,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1131,31 +1072,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1184,31 +1115,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1237,19 +1158,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1265,7 +1178,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1294,19 +1206,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1322,7 +1226,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1351,19 +1254,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1379,7 +1274,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1408,31 +1302,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1461,35 +1345,26 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
           <t>seksi B</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1518,19 +1393,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1546,7 +1413,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1575,19 +1441,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1603,7 +1461,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1632,19 +1489,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1660,7 +1509,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1689,19 +1537,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1717,7 +1557,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1746,19 +1585,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1774,7 +1605,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1803,19 +1633,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1831,7 +1653,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1860,31 +1681,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1913,31 +1724,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1966,19 +1767,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1994,7 +1787,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2023,31 +1815,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2076,19 +1858,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -2104,7 +1878,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2133,31 +1906,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2186,35 +1949,26 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
           <t>seksi A/B</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2243,19 +1997,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -2271,7 +2017,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2300,31 +2045,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2353,31 +2088,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2406,19 +2131,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -2434,7 +2151,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2463,31 +2179,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2516,19 +2222,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -2544,7 +2242,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2591,31 +2288,26 @@
       <c r="J36" t="n">
         <v>1</v>
       </c>
-      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
           <t>IBT 150/70 kV</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2644,31 +2336,21 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2697,31 +2379,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2750,31 +2422,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2803,31 +2465,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2856,19 +2508,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -2884,7 +2528,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2913,31 +2556,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2984,15 +2617,11 @@
       <c r="J43" t="n">
         <v>1</v>
       </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -3008,7 +2637,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -3055,15 +2683,11 @@
       <c r="J44" t="n">
         <v>1</v>
       </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -3079,7 +2703,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3108,31 +2731,21 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3161,31 +2774,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3214,31 +2817,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3267,31 +2860,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3320,31 +2903,21 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3373,19 +2946,11 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -3401,7 +2966,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3430,19 +2994,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -3458,7 +3014,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3487,19 +3042,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -3515,7 +3062,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -3544,23 +3090,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
           <t>seksi A/B</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -3576,7 +3115,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -3605,19 +3143,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -3633,7 +3163,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -3662,19 +3191,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -3690,7 +3211,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -3719,19 +3239,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -3747,7 +3259,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -3776,31 +3287,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3907,7 +3408,6 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Outlet PLTU Gresik</t>
@@ -3928,7 +3428,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>1</v>
       </c>
@@ -3942,8 +3441,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -3960,13 +3457,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>SUTT Gresik - Gresik Lama</t>
@@ -3987,7 +3482,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>2</v>
       </c>
@@ -4001,8 +3495,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -4019,7 +3511,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -4050,7 +3541,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>2</v>
       </c>
@@ -4064,8 +3554,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -4082,7 +3570,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -4113,7 +3600,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>2</v>
       </c>
@@ -4127,8 +3613,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -4145,7 +3629,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -4176,7 +3659,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>2</v>
       </c>
@@ -4190,8 +3672,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -4208,7 +3688,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -4239,7 +3718,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>2</v>
       </c>
@@ -4253,8 +3731,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -4271,7 +3747,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -4302,7 +3777,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>2</v>
       </c>
@@ -4316,8 +3790,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -4334,7 +3806,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -4365,7 +3836,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>2</v>
       </c>
@@ -4379,8 +3849,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -4397,13 +3865,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>SUTT Bambe - Kepatihan</t>
@@ -4424,7 +3890,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>2</v>
       </c>
@@ -4438,8 +3903,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -4456,13 +3919,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>SUTT Bambe - Undaan</t>
@@ -4483,7 +3944,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>2</v>
       </c>
@@ -4497,8 +3957,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -4515,7 +3973,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -4546,7 +4003,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>2</v>
       </c>
@@ -4560,8 +4016,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -4578,13 +4032,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>12</v>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>SUTT Tandes - Gunungsari</t>
@@ -4605,7 +4057,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>2</v>
       </c>
@@ -4619,8 +4070,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -4637,13 +4086,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>13</v>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
           <t>SUTT Kepatihan - Rungkut</t>
@@ -4664,7 +4111,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>2</v>
       </c>
@@ -4678,8 +4124,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -4696,7 +4140,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -4727,7 +4170,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>2</v>
       </c>
@@ -4741,8 +4183,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -4759,13 +4199,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>15</v>
       </c>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
           <t>SUTT Kalang - Surabaya Selatan</t>
@@ -4786,7 +4224,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>2</v>
       </c>
@@ -4800,8 +4237,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -4818,7 +4253,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -4849,7 +4283,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>2</v>
       </c>
@@ -4863,8 +4296,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -4881,13 +4312,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
         <v>17</v>
       </c>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
           <t>SUTT Gubeng - Hayam Jaya</t>
@@ -4908,7 +4337,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>2</v>
       </c>
@@ -4922,8 +4350,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -4940,13 +4366,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
         <v>18</v>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
           <t>SUTT Surabaya Selatan - Kesari</t>
@@ -4967,7 +4391,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>2</v>
       </c>
@@ -4981,8 +4404,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -4999,13 +4420,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
         <v>19</v>
       </c>
-      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
           <t>SUTT Sukolilo - Wonokromo</t>
@@ -5026,7 +4445,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>2</v>
       </c>
@@ -5040,8 +4458,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -5058,7 +4474,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -5089,7 +4504,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
         <v>2</v>
       </c>
@@ -5103,8 +4517,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -5121,13 +4533,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
         <v>21</v>
       </c>
-      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
           <t>SUTT Hayam Jaya - Kejuron</t>
@@ -5148,7 +4558,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>2</v>
       </c>
@@ -5162,8 +4571,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -5180,13 +4587,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
         <v>22</v>
       </c>
-      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
           <t>SUTT Nganggel - Simpang</t>
@@ -5207,7 +4612,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>2</v>
       </c>
@@ -5221,8 +4625,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -5239,7 +4641,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -5270,7 +4671,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>2</v>
       </c>
@@ -5284,8 +4684,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -5302,13 +4700,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
         <v>24</v>
       </c>
-      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
           <t>SUTT Gresik Lama - Altap</t>
@@ -5329,7 +4725,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
         <v>2</v>
       </c>
@@ -5343,8 +4738,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -5361,13 +4754,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
         <v>25</v>
       </c>
-      <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
           <t>SUTT Gresik Lama - Segoromadu</t>
@@ -5388,7 +4779,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
         <v>2</v>
       </c>
@@ -5402,8 +4792,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -5420,7 +4808,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -5451,7 +4838,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
         <v>2</v>
       </c>
@@ -5465,8 +4851,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -5483,7 +4867,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -5514,7 +4897,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
         <v>2</v>
       </c>
@@ -5528,8 +4910,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -5546,7 +4926,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -5577,7 +4956,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
         <v>2</v>
       </c>
@@ -5591,8 +4969,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -5609,7 +4985,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -5640,7 +5015,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
         <v>2</v>
       </c>
@@ -5654,8 +5028,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -5672,7 +5044,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -5703,7 +5074,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
         <v>2</v>
       </c>
@@ -5717,8 +5087,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -5735,13 +5103,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
         <v>31</v>
       </c>
-      <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
           <t>SUTT Perak - Petrokimia</t>
@@ -5762,7 +5128,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
         <v>2</v>
       </c>
@@ -5776,8 +5141,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -5794,13 +5157,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
         <v>32</v>
       </c>
-      <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
           <t>SUTT Sukorejo Kreb - Waru</t>
@@ -5821,7 +5182,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
         <v>2</v>
       </c>
@@ -5835,8 +5195,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -5853,13 +5211,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
         <v>33</v>
       </c>
-      <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
           <t>SUTT Gunungsari - Waru</t>
@@ -5880,7 +5236,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
         <v>2</v>
       </c>
@@ -5894,8 +5249,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -5912,7 +5265,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -5943,7 +5295,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
         <v>2</v>
       </c>
@@ -5957,8 +5308,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -5975,7 +5324,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -6006,7 +5354,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
         <v>2</v>
       </c>
@@ -6020,8 +5367,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -6038,13 +5383,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
         <v>36</v>
       </c>
-      <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
           <t>SUTT Buduran - New Buduran</t>
@@ -6065,7 +5408,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
         <v>2</v>
       </c>
@@ -6079,8 +5421,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -6097,13 +5437,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
         <v>37</v>
       </c>
-      <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
           <t>SUTT New Buduran - Sidoarjo</t>
@@ -6124,7 +5462,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
         <v>2</v>
       </c>
@@ -6138,8 +5475,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -6156,13 +5491,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
         <v>38</v>
       </c>
-      <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
           <t>SUTT 70 kV Buduran - Sedati</t>
@@ -6183,7 +5516,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
         <v>2</v>
       </c>
@@ -6197,8 +5529,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -6215,7 +5545,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -6246,7 +5575,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
         <v>2</v>
       </c>
@@ -6260,8 +5588,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -6278,7 +5604,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -6309,7 +5634,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
         <v>2</v>
       </c>
@@ -6323,8 +5647,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -6341,7 +5663,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -6372,7 +5693,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
         <v>2</v>
       </c>
@@ -6386,8 +5706,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -6404,7 +5722,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -6435,7 +5752,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
         <v>2</v>
       </c>
@@ -6449,8 +5765,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -6467,7 +5781,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -6498,7 +5811,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
         <v>2</v>
       </c>
@@ -6512,8 +5824,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -6530,7 +5840,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6561,7 +5870,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
         <v>2</v>
       </c>
@@ -6575,8 +5883,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -6593,13 +5899,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
         <v>45</v>
       </c>
-      <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
           <t>SUTT Guluk-Guluk - Sumenep</t>
@@ -6620,7 +5924,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
         <v>2</v>
       </c>
@@ -6634,8 +5937,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -6652,7 +5953,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6721,7 +6021,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[N-1] IBT 500/150 kV Krian 1,2 (metropolis)berbeban &gt;80% sehingga sudah tidak memenuhi kriteria N-1. Bus Section GITET Krian belum bisa beroperasi maksimal sebelum adanya GITET Waru sehingga kesulitan dalam manuver dan pekerjaan</t>
+          <t>[N-1] IBT 500/150 kV Krian 1,2 (metropolis) berbeban &gt;80% sehingga sudah tidak memenuhi kriteria N-1. Bus Section GITET Krian belum bisa beroperasi maksimal sebelum adanya GITET Waru sehingga kesulitan dalam manuver dan pekerjaan</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -6731,12 +6031,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1. Sudah terpasang OLS IBT Krian 1,2 - Gresik 1,2 tahap 1,2,3,4,5 dengan total target sebesar997 MW (Berdasarkan Deklarasi ROB Mei 2026). 2. Pengoperasikan Pembangkitan Gresik sesuai batasanya. 3. Pekerjaan dilakukan pada saat beban rendah</t>
+          <t>1. Sudah terpasang OLS IBT Krian 1,2 - Gresik 1,2 tahap 1,2,3,4,5 dengan total target sebesar 997 MW (Berdasarkan Deklarasi ROB Mei 2026). 2. Pengoperasikan Pembangkitan Gresik sesuai batasanya. 3. Pekerjaan dilakukan pada saat beban rendah</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1. Percepatan penyelesaian GISTET 500 kV Waru beserta line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2025, informasi terupdate COD Januari 2027).Note :Terkait dengan beroperasinya GITET 500 kV Waru, pembangkit 150 kV Gresik termasuk energi primer masih sangat dibutuhkan dengan mempertimbangkan kenaikan beban dan keandalan pada masing- masing subsistem. 2. Pembangunan SUTET 500 kV Krian - Waru. (BerdasarkanRUPTL 2025 - 2034, CODTahun 2025, MundurCOD 2028). 3. Percepatan Pembangunan GITET 500 kV Ngoro dan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027. 4. Pembangunan GITET 500 kV Surabaya Selatan dan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). 5. Pembangunan GITET 500 kV Kalanganyar dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027)</t>
+          <t>Jangka Pendek : 1. Percepatan penyelesaian GISTET 500 kV Waru beserta line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2025, informasi terupdate COD Januari 2027). Note :Terkait dengan beroperasinya GITET 500 kV Waru, pembangkit 150 kV Gresik termasuk energi primer masih sangat dibutuhkan dengan mempertimbangkan kenaikan beban dan keandalan pada masing- masing subsistem. 2. Pembangunan SUTET 500 kV Krian - Waru. (Berdasarkan RUPTL 2025 - 2034, CODTahun 2025, Mundur COD 2028). 3. Percepatan Pembangunan GITET 500 kV Ngoro dan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027. 4. Pembangunan GITET 500 kV Surabaya Selatan dan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). 5. Pembangunan GITET 500 kV Kalanganyar dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027)</t>
         </is>
       </c>
     </row>
@@ -6761,17 +6061,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.Overload pada IBT apabila trip 1 IBT. 2.Kesulitan saat melakukan pemeliharaan</t>
+          <t>1. Overload pada IBT apabila trip 1 IBT. 2. Kesulitan saat melakukan pemeliharaan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1.Sudah terpasang OLS IBT Krian 1,2-Gresik 1,2 tahap 1,2,3,4,5 dengan total target sebesar997 MW (Berdasarkan Deklarasi ROB Mei 2026). 2.Pekerjaan dilakukan pada saat beban rendah</t>
+          <t>1. Sudah terpasang OLS IBT Krian 1,2 -Gresik 1,2 tahap 1,2,3,4,5 dengan total target sebesar 997 MW (Berdasarkan Deklarasi ROB Mei 2026). 2. Pekerjaan dilakukan pada saat beban rendah</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>JangkaPendek: 1. Percepatan penyelesaian GISTET 500 kV Waru beserta line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2025, informasi terupdate COD Januari 2027). Note :Terkait dengan beroperasinya GITET 500 kV Waru, pembangkit 150 kV Gresik termasuk energi primer masih sangat dibutuhkan dengan mempertimbangkan Usulan / Solusi kenaikan beban dan keandalan pada masing- masing subsistem. 2. Pembangunan SUTET 500 kV Krian - Waru. (BerdasarkanRUPTL 2025 - 2034, CODTahun2025, MundurCOD 2028). 3. PenambahanBattery Energy Storage System(BESS) sebesar 100 MW dan PLTS sebesar 150 MWdi Pulau Madura (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 4. Pembangunan PLTS 150 kV dan BESS dengan total 100 MW di GI Guluk-Guluk (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). 5. Pembangunan PLTB 150 kV dengan total 100 MW di Sumenep (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). 6. Pembangunan GITET 500 kV Surabaya Selatan dan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). 7. Pembangunan GITET 500 kV Kalanganyar dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027)</t>
+          <t>Jangka Pendek: 1. Percepatan penyelesaian GISTET 500 kV Waru beserta line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2025, informasi terupdate COD Januari 2027). Note :Terkait dengan beroperasinya GITET 500 kV Waru, pembangkit 150 kV Gresik termasuk energi primer masih sangat dibutuhkan dengan mempertimbangkan Usulan / Solusi kenaikan beban dan keandalan pada masing- masing subsistem. 2. Pembangunan SUTET 500 kV Krian - Waru. (Berdasarkan RUPTL 2025 - 2034, COD Tahun2025, Mundur COD 2028). 3. Penambahan Battery Energy Storage System (BESS) sebesar 100 MW dan PLTS sebesar 150 MWdi Pulau Madura (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 4. Pembangunan PLTS 150 kV dan BESS dengan total 100 MW di GI Guluk-Guluk (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). 5. Pembangunan PLTB 150 kV dengan total 100 MW di Sumenep (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). 6. Pembangunan GITET 500 kV Surabaya Selatan dan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). 7. Pembangunan GITET 500 kV Kalanganyar dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027)</t>
         </is>
       </c>
     </row>
@@ -6801,12 +6101,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1. Dilakukan Splitting/pisah Busbar di GI 150 kV Rungkut. 2. Sudah terpasang OLS SKTT Surabaya Barat (Krian)- Karangpilangtahap 1,2,3 dengan total target 676 MW (Berdasarkan Deklarasi ROB Mei 2026).Dilakukan Splitting di GI Rungkut. 3. Pekerjaan dilakukan pada saat beban rendah atau Mitigasi merekonfigurasi di GI Rungkut</t>
+          <t>1. Dilakukan Splitting/pisah Busbar di GI 150 kV Rungkut. 2. Sudah terpasang OLS SKTT Surabaya Barat (Krian)- Karangpilang tahap 1,2,3 dengan total target 676 MW (Berdasarkan Deklarasi ROB Mei 2026). Dilakukan Splitting di GI Rungkut. 3. Pekerjaan dilakukan pada saat beban rendah atau Mitigasi merekonfigurasi di GI Rungkut</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1. Pembangunan GITET 500 kV Waru dan line bay terkait. (RUPTL 2025-2034, COD di 2025). Note:Terkait dengan beroperasinya GITET 500 kV Waru, pembangkit 150 kV Gresik termasuk energi primer masih sangat dibutuhkan dengan mempertimbangkan kenaikan beban dan keandalan pada masing- masing subsistem. 2. Pembangunan SUTET 500 kV Krian - Waru. (BerdasarkanRUPTL 2025 - Usulan / Solusi 2034, CODTahun2025, MundurCOD 2028). 3. Pembangunan GITET 500 kV Surabaya Selatan dan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). 4. Pembangunan GITET 500 kV Kalanganyar dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027)</t>
+          <t>Jangka Pendek : 1. Pembangunan GITET 500 kV Waru dan line bay terkait. (RUPTL 2025 -2034, COD di 2025). Note :Terkait dengan beroperasinya GITET 500 kV Waru, pembangkit 150 kV Gresik termasuk energi primer masih sangat dibutuhkan dengan mempertimbangkan kenaikan beban dan keandalan pada masing- masing subsistem. 2. Pembangunan SUTET 500 kV Krian - Waru. (Berdasarkan RUPTL 2025 - Usulan / Solusi 2034, COD Tahun2025, Mundur COD 2028). 3. Pembangunan GITET 500 kV Surabaya Selatan dan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). 4. Pembangunan GITET 500 kV Kalanganyar dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027)</t>
         </is>
       </c>
     </row>
@@ -6831,17 +6131,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1. Overload pada SUTT 150 kV Surabaya Barat- Sawahan, SUTT 150 kV Sawahan- Gunung sari, SUTT 150 kV Gunung Sari - Waru apabila trip 1 sirkit pada ruas tersebut. 2. Fleksibilitas operasi dan Keandalan berkurang</t>
+          <t>1. Overload pada SUTT 150 kV Surabaya Barat- Sawahan, SUTT 150 kV Sawahan - Gunung sari, SUTT 150 kV Gunung Sari - Waru apabila trip 1 sirkit pada ruas tersebut. 2. Fleksibilitas operasi dan Keandalan berkurang</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1. Sudah terpasang OLS SUTT Surabaya Barat-Sawahan dengan total target sebesar 134 MW (Berdasarkan Deklarasi ROB Mei 2026). 2. Sudah terpasang OLS SUTTSawahan- Gunungsaridengan total target sebesar463MW (Berdasarkan Deklarasi ROB Mei 2026). 3. SudahterpasangOL S SUTT Gunungsari- warudengan totaltargetsebesar 463 MW (Berdasarkan Deklarasi ROB Mei 2026). 4. Pengaturan pekerjaan pemeliharaan dilaksanakan saat beban rendah</t>
+          <t>1. Sudah terpasang OLS SUTT Surabaya Barat-Sawahan dengan total target sebesar 134 MW (Berdasarkan Deklarasi ROB Mei 2026). 2. Sudah terpasang OLS SUTT Sawahan- Gunungsaridengan total target sebesar 463MW (Berdasarkan Deklarasi ROB Mei 2026). 3. Sudah terpasang OL S SUTT Gunungsari- waru dengan total targetsebesar 463 MW (Berdasarkan Deklarasi ROB Mei 2026). 4. Pengaturan pekerjaan pemeliharaan dilaksanakan saat beban rendah</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1. Percepatan penyelesaian GISTET 500 kV Waru beserta line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2025, informasi terupdate COD Januari 2027). Note :Terkait dengan beroperasinya GITET 500 kV Waru, pembangkit 150 kV Gresik termasuk energi primer masih sangat dibutuhkan dengan mempertimbangkan kenaikan beban dan keandalan pada masing- masing subsistem. 2. Pembangunan SUTET 500 kV Krian - Waru. (BerdasarkanRUPTL 2025 - 2034, CODTahun2025, MundurCOD 2028). 3. Pembangunan GITET 500 kV Surabaya Selatan dan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). 4. Pembangunan GITET 500 kV Kalanganyar dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027)</t>
+          <t>Jangka Pendek : 1. Percepatan penyelesaian GISTET 500 kV Waru beserta line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2025, informasi terupdate COD Januari 2027). Note :Terkait dengan beroperasinya GITET 500 kV Waru, pembangkit 150 kV Gresik termasuk energi primer masih sangat dibutuhkan dengan mempertimbangkan kenaikan beban dan keandalan pada masing- masing subsistem. 2. Pembangunan SUTET 500 kV Krian - Waru. (Berdasarkan RUPTL 2025 - 2034, COD Tahun2025, Mundur COD 2028). 3. Pembangunan GITET 500 kV Surabaya Selatan dan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). 4. Pembangunan GITET 500 kV Kalanganyar dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027)</t>
         </is>
       </c>
     </row>
@@ -6861,7 +6161,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[N-1] Pembebanan SUTT 150 kV Surabaya Barat (Krian)-Darmogrande1,2 dan SUTT 150 kV Darmogrande-Waru 1,2 &gt;70%sehinggatidak memenuhikriteriaN-1</t>
+          <t>[N-1] Pembebanan SUTT 150 kV Surabaya Barat (Krian)-Darmogrande 1,2 dan SUTT 150 kV Darmogrande-Waru 1,2 &gt;70%sehingga tidak memenuhi kriteriaN-1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -6871,12 +6171,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1. Sudah terpasang OLS SUTT Surabaya Barat-Darmogrande dengan total target sebesar 96 MW (Berdasarkan Deklarasi ROB Mei 2026). 2. Sudah terpasang OLS SUTT Waru- Darmogrande dengan total target sebesar73 MW (Berdasarkan Deklarasi ROB Mei 2026). 3. Pengaturan pekerjaan pemeliharaan dilaksanakan saat beban rendah</t>
+          <t>1. Sudah terpasang OLS SUTT Surabaya Barat-Darmogrande dengan total target sebesar 96 MW (Berdasarkan Deklarasi ROB Mei 2026). 2. Sudah terpasang OLS SUTT Waru- Darmogrande dengan total target sebesar 73 MW (Berdasarkan Deklarasi ROB Mei 2026). 3. Pengaturan pekerjaan pemeliharaan dilaksanakan saat beban rendah</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1. Percepatan penyelesaian GISTET 500 kV Waru beserta line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2025, informasi terupdate COD Januari 2027). Note :Terkait dengan beroperasinya GITET 500 kV Waru, pembangkit 150 kV Gresik termasuk energi primer masih sangat dibutuhkan dengan mempertimbangkan kenaikan beban dan keandalan pada masing- masing subsistem. 2. Pembangunan SUTET 500 kV Krian - Waru. (BerdasarkanRUPTL 2025 - 2034, CODTahun2025, MundurCOD 2028). 3. Pembangunan GITET 500 kV Surabaya Selatan dan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). 4. Rekonduktoring SUTT 150 kV Krian - Darmogrande - Waru. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). 5. Pembangunan GITET 500 kV Kalanganyar dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027)</t>
+          <t>Jangka Pendek : 1. Percepatan penyelesaian GISTET 500 kV Waru beserta line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2025, informasi terupdate COD Januari 2027). Note :Terkait dengan beroperasinya GITET 500 kV Waru, pembangkit 150 kV Gresik termasuk energi primer masih sangat dibutuhkan dengan mempertimbangkan kenaikan beban dan keandalan pada masing- masing subsistem. 2. Pembangunan SUTET 500 kV Krian - Waru. (Berdasarkan RUPTL 2025 - 2034, COD Tahun2025, Mundur COD 2028). 3. Pembangunan GITET 500 kV Surabaya Selatan dan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). 4. Rekonduktoring SUTT 150 kV Krian - Darmogrande - Waru. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). 5. Pembangunan GITET 500 kV Kalanganyar dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027)</t>
         </is>
       </c>
     </row>
@@ -6896,7 +6196,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[N-1] Outlet pembangkit di Gresik Baru hanya satu yaitu ke SUTT 150 kV Gresik baru-Tandes dan sudah berbeban &gt;60% sehingga tidak memenuhi kriteriaN-1</t>
+          <t>[N-1] Outlet pembangkit di Gresik Baru hanya satu yaitu ke SUTT 150 kV Gresik baru-Tandes dan sudah berbeban &gt;60% sehingga tidak memenuhi kriteria N-1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -6911,7 +6211,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1. Percepatan penyelesaian GISTET 500 kV Waru beserta line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2025, informasi terupdate COD Januari 2027). Note :Terkait dengan beroperasinya GITET 500 kV Waru, pembangkit 150 kV Gresik termasuk energi primer masih sangat dibutuhkan dengan mempertimbangkan kenaikan beban dan Usulan / Solusi keandalan pada masing- masing subsistem. 2. Pembangunan SUTET 500 kV Krian - Waru. (BerdasarkanRUPTL 2025 - 2034, CODTahun2025, MundurCOD 2028). 3. PenambahanBattery Energy Storage System(BESS) sebesar 100 MW dan PLTS sebesar 150 MWdi Pulau Madura (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 4. Pembangunan PLTS 150 kV dan BESS dengan total 100 MW di GI Guluk-Guluk (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). 5. Pembangunan PLTB 150 kV dengan total 100 MW di Sumenep (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). 6. Pembangunan PLTS 150 kV dengan Total 50 MW di GI Sumenep (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2028). 7. Percepatan Pembangunan SUTT 150 kV Gresik- Sawahan. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2028). Jangka Menengah: 8. PenambahanBattery Energy Storage System(BESS) Smothing sebesar 400 MW di Pulau Madura (mengikuti PLTS Sumenep). Jangka Panjang : 9. PenambahanBattery Energy Storage System(BESS) Smothing sebesar 150 MW di Pulau Madura (mengikuti PLTS Sumenep) (Berdasarkan RUPTL 2025 - 2034, COD Diluar RUPTL 2039). 10.PenambahanBattery Energy Storage System(BESS) Smothing sebesar 1.000 MW di Pulau Madura Usulan / Solusi (Berdasarkan RUPTL 2025 - 2034, COD Diluar RUPTL 2039)</t>
+          <t>Jangka Pendek : 1. Percepatan penyelesaian GISTET 500 kV Waru beserta line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2025, informasi terupdate COD Januari 2027). Note :Terkait dengan beroperasinya GITET 500 kV Waru, pembangkit 150 kV Gresik termasuk energi primer masih sangat dibutuhkan dengan mempertimbangkan kenaikan beban dan Usulan / Solusi keandalan pada masing- masing subsistem. 2. Pembangunan SUTET 500 kV Krian - Waru. (Berdasarkan RUPTL 2025 - 2034, COD Tahun2025, Mundur COD 2028). 3. Penambahan Battery Energy Storage System (BESS) sebesar 100 MW dan PLTS sebesar 150 MWdi Pulau Madura (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 4. Pembangunan PLTS 150 kV dan BESS dengan total 100 MW di GI Guluk-Guluk (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). 5. Pembangunan PLTB 150 kV dengan total 100 MW di Sumenep (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). 6. Pembangunan PLTS 150 kV dengan Total 50 MW di GI Sumenep (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2028). 7. Percepatan Pembangunan SUTT 150 kV Gresik- Sawahan. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2028). Jangka Menengah : 8. Penambahan Battery Energy Storage System (BESS) Smothing sebesar 400 MW di Pulau Madura (mengikuti PLTS Sumenep). Jangka Panjang : 9. Penambahan Battery Energy Storage System (BESS) Smothing sebesar 150 MW di Pulau Madura (mengikuti PLTS Sumenep) (Berdasarkan RUPTL 2025 - 2034, COD Diluar RUPTL 2039). 10. PenambahanBattery Energy Storage System (BESS) Smothing sebesar 1.000 MW di Pulau Madura Usulan / Solusi (Berdasarkan RUPTL 2025 - 2034, COD Diluar RUPTL 2039)</t>
         </is>
       </c>
     </row>
@@ -6931,7 +6231,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[N-1] Aliran daya dari PLTU Gresik cenderung melewati GI Sambikerep sehingga pembebanan &gt;60% dan mengakibatkanSUTT 150 kV Gresik lama- Sambikerep tidak memenuhikriteriaN-1</t>
+          <t>[N-1] Aliran daya dari PLTU Gresik cenderung melewati GI Sambikerep sehingga pembebanan &gt;60% dan mengakibatkan SUTT 150 kV Gresik lama- Sambikerep tidak memenuhi kriteriaN-1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -6946,7 +6246,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1. Percepatan penyelesaian GISTET 500 kV Waru beserta line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2025, informasi terupdate COD Januari 2027). Note :Terkait dengan beroperasinya GITET 500 kV Waru, pembangkit 150 kV Gresik termasuk energi primer masih sangat dibutuhkan dengan mempertimbangkan kenaikan beban dan keandalan pada masing- masing subsistem. 2. Pembangunan SUTET 500 kV Krian - Waru. (BerdasarkanRUPTL 2025 - 2034, CODTahun2025, MundurCOD 2028). 3. Pembangunan GITET 500 kV Surabaya Selatan dan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). 4. Pembangunan GITET 500 kV Kalanganyar dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027)</t>
+          <t>Jangka Pendek : 1. Percepatan penyelesaian GISTET 500 kV Waru beserta line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2025, informasi terupdate COD Januari 2027). Note :Terkait dengan beroperasinya GITET 500 kV Waru, pembangkit 150 kV Gresik termasuk energi primer masih sangat dibutuhkan dengan mempertimbangkan kenaikan beban dan keandalan pada masing- masing subsistem. 2. Pembangunan SUTET 500 kV Krian - Waru. (Berdasarkan RUPTL 2025 - 2034, COD Tahun2025, Mundur COD 2028). 3. Pembangunan GITET 500 kV Surabaya Selatan dan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). 4. Pembangunan GITET 500 kV Kalanganyar dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027)</t>
         </is>
       </c>
     </row>
@@ -6966,7 +6266,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[N-1] Pembebanan SUTT 150 kV Tandes-Sawahan &gt;60% sehingga tidak memenuhi kriteriaN-1</t>
+          <t>[N-1] Pembebanan SUTT 150 kV Tandes-Sawahan &gt;60% sehingga tidak memenuhi kriteria N-1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -6976,12 +6276,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1. Sudah terpasang OLS SUTT Tandes- Sawahan dengan total target sebesar135 MW (Berdasarkan Deklarasi ROB Mei 2026). 2. Pengaturan pekerjaan pemeliharaan dilaksanakan saat beban rendah</t>
+          <t>1. Sudah terpasang OLS SUTT Tandes- Sawahan dengan total target sebesar 135 MW (Berdasarkan Deklarasi ROB Mei 2026). 2. Pengaturan pekerjaan pemeliharaan dilaksanakan saat beban rendah</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1. Percepatan penyelesaian GISTET 500 kV Waru beserta line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2025, informasi terupdate COD Januari 2027). Note :Terkait dengan beroperasinya GITET 500 kV Waru, pembangkit 150 kV Gresik termasuk energi primer masih sangat dibutuhkan dengan mempertimbangkan kenaikan beban dan keandalan pada masing- masing subsistem. Usulan / Solusi 2. Pembangunan SUTET 500 kV Krian - Waru. (BerdasarkanRUPTL 2025 - 2034, CODTahun2025, MundurCOD 2028). 3. Percepatan Pembangunan proyek SUTT Gresik- Sawahan (RUPTL 2025- 2034, COD di 2028). JangkaMenengah: 4. Rekonduktoring SUTT 150 kV Tandes - Sawahan. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2029)</t>
+          <t>Jangka Pendek : 1. Percepatan penyelesaian GISTET 500 kV Waru beserta line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2025, informasi terupdate COD Januari 2027). Note :Terkait dengan beroperasinya GITET 500 kV Waru, pembangkit 150 kV Gresik termasuk energi primer masih sangat dibutuhkan dengan mempertimbangkan kenaikan beban dan keandalan pada masing- masing subsistem. Usulan / Solusi 2. Pembangunan SUTET 500 kV Krian - Waru. (Berdasarkan RUPTL 2025 - 2034, COD Tahun2025, Mundur COD 2028). 3. Percepatan Pembangunan proyek SUTT Gresik- Sawahan (RUPTL 2025- 2034, COD di 2028). Jangka Menengah: 4. Rekonduktoring SUTT 150 kV Tandes - Sawahan. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2029)</t>
         </is>
       </c>
     </row>
@@ -7001,7 +6301,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[BELUM_DITETAPKAN] Kopel 150 kV GI Sawahan dibuka untuk spliting SS Kriandan SS Gresik</t>
+          <t>[BELUM_DITETAPKAN] Kopel 150 kV GI Sawahan dibuka untuk spliting SS Krian dan SS Gresik</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -7016,7 +6316,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1. Usulan pembangunan Bus Section di GI Sawahan (diusulkan COD masuk di 2026). 2. Pembangunan GI 150 kV Sawahan II dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2028)</t>
+          <t>Jangka Pendek : 1. Usulan pembangunan Bus Section di GI Sawahan (diusulkan COD masuk di 2026). 2. Pembangunan GI 150 kV Sawahan II dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2028)</t>
         </is>
       </c>
     </row>
@@ -7046,12 +6346,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.Sudah terpasang OLS SUTT Rungkut- Karangpilang, dengan total target16 MW (Berdasarkan Deklarasi ROB Mei 2026). 2.Dilakukan Splitting di GI Rungkut. 3.Pekerjaan dilakukan pada saat beban rendah atau merekonfigurasi di GI Rungkut</t>
+          <t>1. Sudah terpasang OLS SUTT Rungkut- Karangpilang , dengan total target 16 MW (Berdasarkan Deklarasi ROB Mei 2026). 2. Dilakukan Splitting di GI Rungkut. 3. Pekerjaan dilakukan pada saat beban rendah atau merekonfigurasi di GI Rungkut</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1. Percepatan penyelesaian GISTET 500 kV Waru beserta line bay terkait. (Berdasarkan RUPTL 2025- 2034, COD Tahun 2025, informasi terupdate COD Januari 2027).Note :Terkait dengan beroperasinya GITET 500 kV Waru, pembangkit 150 kV Gresik termasuk energi primer masih sangat dibutuhkan dengan mempertimbangkan kenaikan beban dan keandalan pada masing- masing subsistem. 2. Pembangunan SUTET 500 kV Krian - Waru. (BerdasarkanRUPTL 2025- 2034, CODTahun2025, MundurCOD 2028). 3. Pembangunan GITET 500 kV Surabaya Selatan dan line bay terkait. (Berdasarkan RUPTL 2025- 2034, COD Tahun 2027). Usulan / Solusi 4. Pembangunan GITET 500 kV Kalanganyar dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027)</t>
+          <t>Jangka Pendek : 1. Percepatan penyelesaian GISTET 500 kV Waru beserta line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2025, informasi terupdate COD Januari 2027). Note :Terkait dengan beroperasinya GITET 500 kV Waru, pembangkit 150 kV Gresik termasuk energi primer masih sangat dibutuhkan dengan mempertimbangkan kenaikan beban dan keandalan pada masing- masing subsistem. 2. Pembangunan SUTET 500 kV Krian - Waru. (Berdasarkan RUPTL 2025 - 2034, COD Tahun2025, Mundur COD 2028). 3. Pembangunan GITET 500 kV Surabaya Selatan dan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). Usulan / Solusi 4. Pembangunan GITET 500 kV Kalanganyar dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027)</t>
         </is>
       </c>
     </row>
@@ -7071,7 +6371,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>[N-1] Pembebanan SUTT 150 kV Sambikerep-Waru &gt;65% sehingga tidak memenuhi kriteriaN-1</t>
+          <t>[N-1] Pembebanan SUTT 150 kV Sambikerep-Waru &gt;65% sehingga tidak memenuhi kriteria N-1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -7081,12 +6381,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1. Sudah terpasang OLS SUTT Sambikerep-Waru dengan total target 463 MW(Berdasarkan Deklarasi ROB Mei 2026). 2. Pekerjaan SUTT 150 kV Gresik lama - Sambikerep dilaksanakan dengan melakukan pengaturan Pembangkitan Gresik Lama sesuai dengan kebutuhan dan dilaksanakan pada saat beban rendah</t>
+          <t>1. Sudah terpasang OLS SUTT Sambikerep-Waru dengan total target 463 MW (Berdasarkan Deklarasi ROB Mei 2026). 2. Pekerjaan SUTT 150 kV Gresik lama - Sambikerep dilaksanakan dengan melakukan pengaturan Pembangkitan Gresik Lama sesuai dengan kebutuhan dan dilaksanakan pada saat beban rendah</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>JangkaPendek: 1. Percepatan penyelesaian GISTET 500 kV Waru beserta line bay terkait. (Berdasarkan RUPTL 2025- 2034, COD Tahun 2025, informasi terupdate COD Januari 2027).Note :Terkait dengan beroperasinya GITET 500 kV Waru, pembangkit 150 kV Gresik termasuk energi primer masih sangat dibutuhkan dengan mempertimbangkan kenaikan beban dan keandalan pada masing- masing subsistem. 2. Pembangunan SUTET 500 kV Krian - Waru. (BerdasarkanRUPTL 2025- 2034, CODTahun2025. 3. Pembangunan GITET 500 kV Surabaya Selatan dan line bay terkait. (Berdasarkan RUPTL 2025- 2034, COD Tahun 2027). 4. Pembangunan GITET 500 kV Kalanganyar dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027)</t>
+          <t>Jangka Pendek: 1. Percepatan penyelesaian GISTET 500 kV Waru beserta line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2025, informasi terupdate COD Januari 2027). Note :Terkait dengan beroperasinya GITET 500 kV Waru, pembangkit 150 kV Gresik termasuk energi primer masih sangat dibutuhkan dengan mempertimbangkan kenaikan beban dan keandalan pada masing- masing subsistem. 2. Pembangunan SUTET 500 kV Krian - Waru. (Berdasarkan RUPTL 2025 - 2034, COD Tahun2025. 3. Pembangunan GITET 500 kV Surabaya Selatan dan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). 4. Pembangunan GITET 500 kV Kalanganyar dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027)</t>
         </is>
       </c>
     </row>
@@ -7106,7 +6406,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[N-1] Pembebanan SUTT 150 kV Rungkut-Waru berbeban&gt;80%sehingga tidak memenuhi kriteria N-1</t>
+          <t>[N-1] Pembebanan SUTT 150 kV Rungkut-Waru berbeban &gt;80%sehingga tidak memenuhi kriteria N-1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -7116,12 +6416,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1. Sudah terpasang OLS SUTT Rungkut- Waru dengan total target sebesar676MW (B erdasarkan Deklarasi ROB Mei 2026). 2. Pekerjaan dilaksanakan pada saat beban rendah</t>
+          <t>1. Sudah terpasang OLS SUTT Rungkut- Waru dengan total target sebesar 676MW (B erdasarkan Deklarasi ROB Mei 2026). 2. Pekerjaan dilaksanakan pada saat beban rendah</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>JangkaPendek: 1. Percepatan penyelesaian GISTET 500 kV Waru beserta line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2025, informasi terupdate COD Januari 2027).Note :Terkait dengan beroperasinya GITET 500 kV Waru, pembangkit 150 kV Gresik termasuk energi primer masih sangat dibutuhkan dengan mempertimbangkan kenaikan beban dan Usulan / Solusi keandalan pada masing- masing subsistem. 2. Pembangunan SUTET 500 kV Krian - Waru. (BerdasarkanRUPTL 2025 - 2034, CODTahun2025, MundurCOD 2028). 3. Pembangunan GITET 500 kV Surabaya Selatan dan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). 4. Pembangunan GITET 500 kV Kalanganyar dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). JangkaMenengah: 5. Pembangunan SUTT 150 kV Kupang-Wonokromo. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2030). 6. Pembangunan SUTT 150 kV Simpang-Undaan. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2030). 7. Pembangunan SUTT 150 kV Kenjeran-Undaan. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2030)</t>
+          <t>Jangka Pendek: 1. Percepatan penyelesaian GISTET 500 kV Waru beserta line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2025, informasi terupdate COD Januari 2027). Note :Terkait dengan beroperasinya GITET 500 kV Waru, pembangkit 150 kV Gresik termasuk energi primer masih sangat dibutuhkan dengan mempertimbangkan kenaikan beban dan Usulan / Solusi keandalan pada masing- masing subsistem. 2. Pembangunan SUTET 500 kV Krian - Waru. (Berdasarkan RUPTL 2025 - 2034, COD Tahun2025, Mundur COD 2028). 3. Pembangunan GITET 500 kV Surabaya Selatan dan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). 4. Pembangunan GITET 500 kV Kalanganyar dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). Jangka Menengah: 5. Pembangunan SUTT 150 kV Kupang-Wonokromo. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2030). 6. Pembangunan SUTT 150 kV Simpang-Undaan. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2030). 7. Pembangunan SUTT 150 kV Kenjeran-Undaan. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2030)</t>
         </is>
       </c>
     </row>
@@ -7151,12 +6451,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1.Sudah terpasang OLS di ruas SUTT Waru- Buduran ; Waru- GIS Buduran dengan total target sebesar 159 MW (Berdasarkan Deklarasi ROB Mei 2026). 2.Pekerjaan hanya bisa dilaksanakan pada saat beban rendah dan persetujuan dari konsumen</t>
+          <t>1. Sudah terpasang OLS di ruas SUTT Waru- Buduran ; Waru- GIS Buduran dengan total target sebesar 159 MW (Berdasarkan Deklarasi ROB Mei 2026). 2. Pekerjaan hanya bisa dilaksanakan pada saat beban rendah dan persetujuan dari konsumen</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1. Percepatan Pembangunan GITET 500 kV Ngoro dan SUTT 150 kV Ngoro - New Porong. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027untuk GITET, dan 2028 untuk SUTT, informasi terupdate COD Des 2027 (GITET Ngoro) dan 2028 (SUTT). 2. Pembangunan GITET 500 kV Kalanganyar dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). 3. Rekonduktoring SUTT 150 kV Waru - Buduran - GIS buduran. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2028)</t>
+          <t>Jangka Pendek : 1. Percepatan Pembangunan GITET 500 kV Ngoro dan SUTT 150 kV Ngoro - New Porong. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027 untuk GITET, dan 2028 untuk SUTT, informasi terupdate COD Des 2027 (GITET Ngoro) dan 2028 (SUTT). 2. Pembangunan GITET 500 kV Kalanganyar dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). 3. Rekonduktoring SUTT 150 kV Waru - Buduran - GIS buduran. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2028)</t>
         </is>
       </c>
     </row>
@@ -7191,7 +6491,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Jangka Pendek: Usulan / Solusi Usulan memindah seluruh bay GI Buduran ke GIS New Buduran (Usulan COD 2026)</t>
+          <t>Jangka Pendek : Usulan / Solusi Usulan memindah seluruh bay GI Buduran ke GIS New Buduran (Usulan COD 2026)</t>
         </is>
       </c>
     </row>
@@ -7226,7 +6526,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>JangkaPendek: Usulan baru penambahan Busbar di GI 70 kV Maspion menjadi Double Busbar. (diusulkan COD masuk di 2026).Penambahan Busbar ini terkendala dengan lokasi lahan GI 70 kV Maspion ada di dalam Kawasan pabrik, sehingga workability pekerjaan membutuhkan ijin dari Pabrik Maspion. Butuh padam saat penyambungan jika pekerjaan Double Busbar sudah selesai</t>
+          <t>Jangka Pendek: Usulan baru penambahan Busbar di GI 70 kV Maspion menjadi Double Busbar. (diusulkan COD masuk di 2026).Penambahan Busbar ini terkendala dengan lokasi lahan GI 70 kV Maspion ada di dalam Kawasan pabrik, sehingga workability pekerjaan membutuhkan ijin dari Pabrik Maspion. Butuh padam saat penyambungan jika pekerjaan Double Busbar sudah selesai</t>
         </is>
       </c>
     </row>
@@ -7251,17 +6551,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.Overload pada SUTT 150 kV Rungkut-Sukolilo apabila trip 1 sirkit pada ruas tersebut. 2.Kesulitan dalam melakukan pemeliharaan</t>
+          <t>1. Overload pada SUTT 150 kV Rungkut-Sukolilo apabila trip 1 sirkit pada ruas tersebut. 2. Kesulitan dalam melakukan pemeliharaan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1.Sudah terpasang OLS di ruas Rungkut- Sukolilo dan dengan total target sebesar 109 MW (Berdasarkan Deklarasi ROB Mei 2026). 2.Pekerjaan hanya bisa dilaksanakan pada saat beban rendah</t>
+          <t>1. Sudah terpasang OLS di ruas Rungkut- Sukolilo dan dengan total target sebesar 109 MW (Berdasarkan Deklarasi ROB Mei 2026). 2.Pekerjaan hanya bisa dilaksanakan pada saat beban rendah</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Jangka Pendek : 1. Percepatan PembangunanSUTT 150 kVKalisari-Kedinding. (Berdasarkan RUPTL 2025- 2034, COD Tahun 2027). 2. PenambahanBattery Energy Storage System(BESS) sebesar 100 MW dan PLTS sebesar 150 MWdi Pulau Madura (Berdasarkan RUPTL 2025- 2034, COD Tahun 2026). Jangka Menegah : 3. Pembangunan SUTT 150 kV Kupang-Wonokromo. (Berdasarkan RUPTL 2025- 2034, COD Tahun 2030). 4. Pembangunan SUTT 150 kV Simpang-Undaan. (Berdasarkan RUPTL 2025- 2034, COD Tahun 2030). 5. Pembangunan SUTT 150 kV Kenjeran-Undaan. (Berdasarkan RUPTL 2025- 2034, COD Tahun 2030)</t>
+          <t>Jangka Pendek : 1. Percepatan Pembangunan SUTT 150 kV Kalisari-Kedinding. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). 2. Penambahan Battery Energy Storage System (BESS) sebesar 100 MW dan PLTS sebesar 150 MWdi Pulau Madura (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). Jangka Menegah : 3. Pembangunan SUTT 150 kV Kupang-Wonokromo. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2030). 4. Pembangunan SUTT 150 kV Simpang-Undaan. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2030). 5. Pembangunan SUTT 150 kV Kenjeran-Undaan. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2030)</t>
         </is>
       </c>
     </row>
@@ -7281,22 +6581,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>[N-1] Pembebanan SUTT 150 kV Sukolilo-Kenjeran sudah &gt;55% pada saat Konfigurasi Spliting Madurasehingga tidak memenuhi kriteriaN-1</t>
+          <t>[N-1] Pembebanan SUTT 150 kV Sukolilo-Kenjeran sudah &gt;55% pada saat Konfigurasi Spliting Madura sehingga tidak memenuhi kriteria N-1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.Overload pada SUTT 150 kV Sukolilo-Kenjeran apabila trip 1 sirkit pada ruas tersebut saat memasok Madura. 2.Kesulitan dalam melakukan Dampak pemeliharaan saat memasok Madura</t>
+          <t>1. Overload pada SUTT 150 kV Sukolilo-Kenjeran apabila trip 1 sirkit pada ruas tersebut saat memasok Madura. 2. Kesulitan dalam melakukan Dampak pemeliharaan saat memasok Madura</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1.Sudah terpasang OLS di ruas Sukolilo- Kenjeran dengan total target sebesar 53 MW (Berdasarkan Deklarasi ROB Mei 2026). Mitigasi 2.Pekerjaan hanya bisa dilaksanakan pada saat beban rendah</t>
+          <t>1. Sudah terpasang OLS di ruas Sukolilo- Kenjeran dengan total target sebesar 53 MW (Berdasarkan Deklarasi ROB Mei 2026). Mitigasi 2.Pekerjaan hanya bisa dilaksanakan pada saat beban rendah</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Jangka Pendek : 1.Percepatan PembangunanSUTT 150 kVKalisari-Kedinding. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). 2.PenambahanBattery Energy Storage System(BESS) sebesar 100 MW dan PLTS Usulan / Solusi sebesar 150 MWdi Pulau Madura (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). Jangka Menegah : 3.Pembangunan SUTT 150 kV Kupang-Wonokromo. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2030). 4.Pembangunan SUTT 150 kV Simpang-Undaan. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2030). 5.Pembangunan SUTT 150 kV Kenjeran-Undaan. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2030)</t>
+          <t>Jangka Pendek : 1.Percepatan Pembangunan SUTT 150 kV Kalisari-Kedinding. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). 2.Penambahan Battery Energy Storage System (BESS) sebesar 100 MW dan PLTS Usulan / Solusi sebesar 150 MWdi Pulau Madura (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). Jangka Menegah : 3.Pembangunan SUTT 150 kV Kupang-Wonokromo. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2030). 4.Pembangunan SUTT 150 kV Simpang-Undaan. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2030). 5.Pembangunan SUTT 150 kV Kenjeran-Undaan. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2030)</t>
         </is>
       </c>
     </row>
@@ -7326,12 +6626,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1.Sudah terpasang OLS SUTT 150 kV Tandes- Perak dan Tandes- Ujung dengan total target sebesar 257 MW (Berdasarkan Deklarasi ROB Mei 2026). 2.Pekerjaan dilakukan saat beban rendah</t>
+          <t>1. Sudah terpasang OLS SUTT 150 kV Tandes- Perak dan Tandes- Ujung dengan total target sebesar 257 MW (Berdasarkan Deklarasi ROB Mei 2026). 2. Pekerjaan dilakukan saat beban rendah</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Jangka Pendek : 1.Usulan penggantian CT bay di GIS Tandes sesuai dengankemampuan SUTT nya (diusulkan COD masuk di 2026) Kajian operasi belum ada. 2.Rekonduktoring SUTT 150 kV Ujung - Perak. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). Jangka Menengah : 3.Pembangunan SUTT 150 kV Kenjeran-Undaan. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2030)</t>
+          <t>Jangka Pendek : 1. Usulan penggantian CT bay di GIS Tandes sesuai dengan kemampuan SUTT nya (diusulkan COD masuk di 2026) Kajian operasi belum ada. 2.Rekonduktoring SUTT 150 kV Ujung - Perak. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). Jangka Menengah : 3.Pembangunan SUTT 150 kV Kenjeran-Undaan. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2030)</t>
         </is>
       </c>
     </row>
@@ -7391,17 +6691,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.Padam di GI Gilitimur dan sebagianbeban GI Bangkalan bila ruas tersebut trip. Dampak 2.Pembebanan kabel Suramadu tidak seimbang</t>
+          <t>1. Padam di GI Gilitimur dan sebagian beban GI Bangkalan bila ruas tersebut trip. Dampak 2.Pembebanan kabel Suramadu tidak seimbang</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1.Sudah terpasang OLS SUTT 150 kV Kenjeran-Gilitimur dengan total target sebesar 257 MW (Berdasarkan Mitigasi Deklarasi ROB Mei 2026). 2.Pekerjaanhanyabisa dilaksanakanpadasa atbebanrendah, dan dilakukan rekonfigurasi jaringan</t>
+          <t>1. Sudah terpasang OLS SUTT 150 kV Kenjeran-Gilitimur dengan total target sebesar 257 MW (Berdasarkan Mitigasi Deklarasi ROB Mei 2026). 2.Pekerjaanhanya bisa dilaksanakanpadasa atbebanrendah, dan dilakukan rekonfigurasi jaringan</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Jangka Pendek : 1.Normalisasi pasokan arah Madura 4 sirkit Kedinding - Bangkalan (Pembangunan SKTT 150 kV Kedinding-TX Bangkalan. (Berdasarkan Usulan / Solusi RUPTL 2025 - 2034, COD Tahun 2026). 2.Pembangunan Bus Section di GIS 150 kV Kedinding (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 3.PenambahanBattery Energy Storage System(BESS) sebesar 100 MW dan PLTS sebesar 150 MWdi Pulau Madura (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 4.Pembangunan PLTS 150 kV dan BESS dengan total 100 MW di GI Guluk-Guluk (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). 5.Pembangunan PLTB 150 kV dengan total 100 MW di Sumenep (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). 6.Pembangunan PLTS 150 kV dengan Total 50 MW di GI Sumenep (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2028. Jangka Menengah : 7.PenambahanBattery Energy Storage System(BESS) Smothing sebesar 400 MW di Pulau Madura (mengikuti PLTS Sumenep) (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2031). 8.PenambahanBattery Energy Storage System(BESS) Smothing sebesar 150 MW di Pulau Madura (mengikuti PLTS Sumenep) (Berdasarkan RUPTL 2025 - 2034, COD Diluar RUPTL 2039). 9.PenambahanBattery Energy Storage System(BESS) Smothing sebesar 1.000 MW di Pulau Madura (Berdasarkan RUPTL 2025 - 2034, COD Diluar RUPTL 2039)</t>
+          <t>Jangka Pendek : 1. Normalisasi pasokan arah Madura 4 sirkit Kedinding - Bangkalan (Pembangunan SKTT 150 kV Kedinding-TX Bangkalan. (Berdasarkan Usulan / Solusi RUPTL 2025 - 2034, COD Tahun 2026). 2. Pembangunan Bus Section di GIS 150 kV Kedinding (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 3. PenambahanBattery Energy Storage System (BESS) sebesar 100 MW dan PLTS sebesar 150 MWdi Pulau Madura (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 4. Pembangunan PLTS 150 kV dan BESS dengan total 100 MW di GI Guluk-Guluk (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). 5. Pembangunan PLTB 150 kV dengan total 100 MW di Sumenep (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). 6. Pembangunan PLTS 150 kV dengan Total 50 MW di GI Sumenep (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2028. Jangka Menengah : 7. PenambahanBattery Energy Storage System (BESS) Smothing sebesar 400 MW di Pulau Madura (mengikuti PLTS Sumenep) (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2031). 8. PenambahanBattery Energy Storage System (BESS) Smothing sebesar 150 MW di Pulau Madura (mengikuti PLTS Sumenep) (Berdasarkan RUPTL 2025 - 2034, COD Diluar RUPTL 2039). 9. PenambahanBattery Energy Storage System (BESS) Smothing sebesar 1.000 MW di Pulau Madura (Berdasarkan RUPTL 2025 - 2034, COD Diluar RUPTL 2039)</t>
         </is>
       </c>
     </row>
@@ -7436,7 +6736,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Jangka Pendek : Usulan / Solusi 1.Normalisasi pasokan arah Madura 4 sirkit Kedinding - Bangkalan (Pembangunan SKTT 150 kV Kedinding-TX Bangkalan. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 2.Pembangunan Bus Section di GIS 150 kV Kedinding. (Berdasarkan RUPTL 2025 - 2034, COD 2026). 3.Percepatan pembangunan SUTT 150 kV Looping utara Madura. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 4.PenambahanBattery Energy Storage System(BESS) sebesar 100 MW dan PLTS sebesar 150 MWdi Pulau Madura (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 5.Pembangunan PLTS 150 kV dan BESS dengan total 100 MW di GI Guluk-Guluk (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). 6.Pembangunan PLTB 150 kV dengan total 100 MW di Sumenep (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). 7.Pembangunan PLTS 150 kV dengan Total 50 MW di GI Sumenep (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2028). Jangka Menengah : 8.PenambahanBattery Energy Storage System(BESS) Smothing sebesar 400 MW di Pulau Madura (mengikuti PLTS Sumenep) (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2031). 9.Pembangunan PLTGU 150 kV Jawa Bali-4 dengan total 500 MW. Berdasarkan RUPTL 2025-2034 COD Base tahun 2029. Jangka Panjang : Usulan / Solusi 10.PenambahanBattery Energy Storage System(BESS) Smothing sebesar 150 MW di Pulau Madura (mengikuti PLTS Sumenep) (Berdasarkan RUPTL 2025 - 2034, COD Diluar RUPTL 2039). 11.PenambahanBattery Energy Storage System(BESS) Smothing sebesar 1.000 MW di Pulau Madura (Berdasarkan RUPTL 2025 - 2034, COD Diluar RUPTL 2039)</t>
+          <t>Jangka Pendek : Usulan / Solusi 1. Normalisasi pasokan arah Madura 4 sirkit Kedinding - Bangkalan (Pembangunan SKTT 150 kV Kedinding-TX Bangkalan. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 2. Pembangunan Bus Section di GIS 150 kV Kedinding. (Berdasarkan RUPTL 2025 - 2034, COD 2026). 3. Percepatan pembangunan SUTT 150 kV Looping utara Madura. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 4. PenambahanBattery Energy Storage System (BESS) sebesar 100 MW dan PLTS sebesar 150 MWdi Pulau Madura (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 5. Pembangunan PLTS 150 kV dan BESS dengan total 100 MW di GI Guluk-Guluk (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). 6. Pembangunan PLTB 150 kV dengan total 100 MW di Sumenep (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). 7. Pembangunan PLTS 150 kV dengan Total 50 MW di GI Sumenep (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2028). Jangka Menengah : 8. PenambahanBattery Energy Storage System (BESS) Smothing sebesar 400 MW di Pulau Madura (mengikuti PLTS Sumenep) (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2031). 9. Pembangunan PLTGU 150 kV Jawa Bali-4 dengan total 500 MW. Berdasarkan RUPTL 2025-2034 COD Base tahun 2029. Jangka Panjang : Usulan / Solusi 10. PenambahanBattery Energy Storage System (BESS) Smothing sebesar 150 MW di Pulau Madura (mengikuti PLTS Sumenep) (Berdasarkan RUPTL 2025 - 2034, COD Diluar RUPTL 2039). 11. PenambahanBattery Energy Storage System (BESS) Smothing sebesar 1.000 MW di Pulau Madura (Berdasarkan RUPTL 2025 - 2034, COD Diluar RUPTL 2039)</t>
         </is>
       </c>
     </row>
@@ -7471,7 +6771,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Jangka Pendek : 1.Normalisasi pasokan arah Madura 4 sirkit Kedinding - Bangkalan (Pembangunan SKTT 150 kV Kedinding-TX Bangkalan. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 2.PenambahanBattery Energy Storage System(BESS) sebesar 100 MW dan PLTS sebesar 150 MWdi Pulau Madura (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 3.Pembangunan PLTS 150 kV dan BESS dengan total 100 MW di GI Guluk-Guluk (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). 4.Pembangunan PLTB 150 kV dengan total 100 MW di Sumenep (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). 5.Pembangunan PLTS 150 kV dengan Total 50 MW di GI Sumenep (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2028). 6.Pembangunan PLTGU 150 kV Jawa Bali-4 dengan total 500 MW. Berdasarkan RUPTL 2025-2034 COD Base tahun 2029. Jangka Menengah : 7.Pembangunan SUTT 150 kV Kenjeran-Undaan. Usulan / Solusi (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2030). 8.PenambahanBattery Energy Storage System(BESS) Smothing sebesar 400 MW di Pulau Madura (mengikuti PLTS Sumenep) (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2031), Jangka Panjang : 9.PenambahanBattery Energy Storage System(BESS) Smothing sebesar 150 MW di Pulau Madura (mengikuti PLTS Sumenep) (Berdasarkan RUPTL 2025 - 2034, COD Diluar RUPTL 2039). 10.PenambahanBattery Energy Storage System(BESS) Smothing sebesar 1.000 MW di Pulau Madura (Berdasarkan RUPTL 2025 - 2034, COD Diluar RUPTL 2039)</t>
+          <t>Jangka Pendek : 1. Normalisasi pasokan arah Madura 4 sirkit Kedinding - Bangkalan (Pembangunan SKTT 150 kV Kedinding-TX Bangkalan. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 2. PenambahanBattery Energy Storage System (BESS) sebesar 100 MW dan PLTS sebesar 150 MWdi Pulau Madura (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 3. Pembangunan PLTS 150 kV dan BESS dengan total 100 MW di GI Guluk-Guluk (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). 4. Pembangunan PLTB 150 kV dengan total 100 MW di Sumenep (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). 5. Pembangunan PLTS 150 kV dengan Total 50 MW di GI Sumenep (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2028). 6. Pembangunan PLTGU 150 kV Jawa Bali-4 dengan total 500 MW. Berdasarkan RUPTL 2025-2034 COD Base tahun 2029. Jangka Menengah : 7. Pembangunan SUTT 150 kV Kenjeran-Undaan. Usulan / Solusi (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2030). 8. PenambahanBattery Energy Storage System (BESS) Smothing sebesar 400 MW di Pulau Madura (mengikuti PLTS Sumenep) (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2031), Jangka Panjang : 9. PenambahanBattery Energy Storage System (BESS) Smothing sebesar 150 MW di Pulau Madura (mengikuti PLTS Sumenep) (Berdasarkan RUPTL 2025 - 2034, COD Diluar RUPTL 2039). 10. PenambahanBattery Energy Storage System (BESS) Smothing sebesar 1.000 MW di Pulau Madura (Berdasarkan RUPTL 2025 - 2034, COD Diluar RUPTL 2039)</t>
         </is>
       </c>
     </row>
@@ -7491,7 +6791,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>[BELUM_DITETAPKAN] Pembebanan SUTT 150 kV Bangkalan-Sampang berbeban&gt;100%</t>
+          <t>[BELUM_DITETAPKAN] Pembebanan SUTT 150 kV Bangkalan -Sampang berbeban &gt;100%</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -7501,12 +6801,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1.Sudah terpasang OLS di SUTT 150 kV Bangkalan-Sampang dengan total target sebesar 162 MW (Berdasarkan Deklarasi ROB Mei 2026). 2.Distribusi melakukan rekonfigurasi jaringan 20KV untuk memindahkan beban GI 150KV Sampang ke GI 150 kV. bangkalan dan penggunaan Pembangkit Sewa yang disebar di level tegangan 20kV</t>
+          <t>1.Sudah terpasang OLS di SUTT 150 kV Bangkalan-Sampang dengan total target sebesar 162 MW (Berdasarkan Deklarasi ROB Mei 2026). 2.Distribusi melakukan rekonfigurasi jaringan 20KV untuk memindahkan beban GI 150KV Sampang ke GI 150 kV. bangkalan dan penggunaan Pembangkit Sewa yang disebar di level tegangan 20 kV</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Jangka Pendek : 1.Percepatan pembangunan SUTT 150 kV Looping utara Madura. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 2.PenambahanBattery Energy Storage System(BESS) sebesar 100 MW dan PLTS sebesar 150 MWdi Pulau Madura (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 3.Rekonduktoring SUTT 150 kV Bangkalan-Sampang. (Berdasarkan RUPTL 2025- 2034, COD Tahun 2027). 4.Pembangunan PLTS 150 kV dan BESS dengan total 100 MW di GI Guluk-Guluk (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). 5.Pembangunan PLTB 150 kV dengan total 100 MW di Sumenep (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). 6.Pembangunan PLTS 150 kV dengan Total 50 MW di GI Usulan / Solusi Sumenep (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2028). 7.Pembangunan PLTGU 150 kV Jawa Bali-4 dengan total 500 MW. Berdasarkan RUPTL 2025-2034 COD Base tahun 2029.. Jangka Menengah : 8.PenambahanBattery Energy Storage System(BESS) Smothing sebesar 400 MW di Pulau Madura (mengikuti PLTS Sumenep) (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2031). Jangka Panjang : 9. PenambahanBattery Energy Storage System(BESS) Smothing sebesar 150 MW di Pulau Madura (mengikuti PLTS Sumenep) (Berdasarkan RUPTL 2025 - 2034, COD Diluar RUPTL 2039). 10.PenambahanBattery Energy Storage System(BESS) Smothing sebesar 1.000 MW di Pulau Madura (Berdasarkan RUPTL 2025 - 2034, COD Diluar RUPTL 2039)</t>
+          <t>Jangka Pendek : 1. Percepatan pembangunan SUTT 150 kV Looping utara Madura. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 2. PenambahanBattery Energy Storage System (BESS) sebesar 100 MW dan PLTS sebesar 150 MWdi Pulau Madura (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 3. Rekonduktoring SUTT 150 kV Bangkalan-Sampang. (Berdasarkan RUPTL 2025- 2034, COD Tahun 2027). 4. Pembangunan PLTS 150 kV dan BESS dengan total 100 MW di GI Guluk-Guluk (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). 5. Pembangunan PLTB 150 kV dengan total 100 MW di Sumenep (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). 6. Pembangunan PLTS 150 kV dengan Total 50 MW di GI Usulan / Solusi Sumenep (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2028). 7. Pembangunan PLTGU 150 kV Jawa Bali-4 dengan total 500 MW. Berdasarkan RUPTL 2025-2034 COD Base tahun 2029.. Jangka Menengah : 8. PenambahanBattery Energy Storage System (BESS) Smothing sebesar 400 MW di Pulau Madura (mengikuti PLTS Sumenep) (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2031). Jangka Panjang : 9. Penambahan Battery Energy Storage System (BESS) Smothing sebesar 150 MW di Pulau Madura (mengikuti PLTS Sumenep) (Berdasarkan RUPTL 2025 - 2034, COD Diluar RUPTL 2039). 10. PenambahanBattery Energy Storage System (BESS) Smothing sebesar 1.000 MW di Pulau Madura (Berdasarkan RUPTL 2025 - 2034, COD Diluar RUPTL 2039)</t>
         </is>
       </c>
     </row>
@@ -7526,7 +6826,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>[BELUM_DITETAPKAN] Pembebanan SUTT 150 kV Sampang - Pamekasanberbeban &gt;65%</t>
+          <t>[BELUM_DITETAPKAN] Pembebanan SUTT 150 kV Sampang - Pamekasan berbeban &gt;65%</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -7536,12 +6836,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sudah terpasang OLS di SUTT 150kV Sampang- Pamekasan dengan total target sebesar 70MW (Berdasarkan Deklarasi ROB Mei 2026)</t>
+          <t>Sudah terpasang OLS di SUTT 150 kV Sampang- Pamekasan dengan total target sebesar 70 MW (Berdasarkan Deklarasi ROB Mei 2026)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Jangka Pendek : 1.Percepatan pembangunan SUTT 150 kV Looping utara Madura. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 2.PenambahanBattery Energy Storage System(BESS) sebesar 100 MW dan PLTS sebesar 150 MWdi Pulau Madura (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 3.Rekonduktoring SUTT 150 kV Sampang-Pamekasan- Sumenep. (Berdasarkan RUPTL 2025- 2034, COD Tahun 2028). 4.Pembangunan PLTS 150 kV dan BESS dengan total 100 MW di GI Guluk-Guluk Usulan / Solusi (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). 5.Pembangunan PLTB 150 kV dengan total 100 MW di Sumenep (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). 6.Pembangunan PLTS 150 kV dengan Total 50 MW di GI Sumenep (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2028). 7.Pembangunan PLTGU 150 kV Jawa Bali-4 dengan total 500 MW. Berdasarkan RUPTL 2025-2034 COD Base tahun 2029</t>
+          <t>Jangka Pendek : 1. Percepatan pembangunan SUTT 150 kV Looping utara Madura. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 2. PenambahanBattery Energy Storage System (BESS) sebesar 100 MW dan PLTS sebesar 150 MWdi Pulau Madura (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 3. Rekonduktoring SUTT 150 kV Sampang-Pamekasan- Sumenep. (Berdasarkan RUPTL 2025- 2034, COD Tahun 2028). 4. Pembangunan PLTS 150 kV dan BESS dengan total 100 MW di GI Guluk-Guluk Usulan / Solusi (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). 5. Pembangunan PLTB 150 kV dengan total 100 MW di Sumenep (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). 6. Pembangunan PLTS 150 kV dengan Total 50 MW di GI Sumenep (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2028). 7. Pembangunan PLTGU 150 kV Jawa Bali-4 dengan total 500 MW. Berdasarkan RUPTL 2025-2034 COD Base tahun 2029</t>
         </is>
       </c>
     </row>
@@ -7566,7 +6866,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.Drop tegangan yang cukup signifikan di Subsistem Gresik sehingga terjadi komplain konsumen KTT. 2.Terjadi ekskursi tegangan di wilayah Madura</t>
+          <t>1. Drop tegangan yang cukup signifikan di Subsistem Gresik sehingga terjadi komplain konsumen KTT. 2. Terjadi ekskursi tegangan di wilayah Madura</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">

--- a/samples/ss_krian12_gresik_ingest.xlsx
+++ b/samples/ss_krian12_gresik_ingest.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,10 +474,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Multi Pin</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ya</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>Sumber</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Buku Kerawanan SJB 2026 Sec 5.3 (Tabel 5.1, PDF p.180-196); topologi dari Gambar 5.3 Peta Kerawanan (PDF p.179)</t>
         </is>
@@ -494,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U57"/>
+  <dimension ref="A1:U55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -960,17 +972,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Surabaya Barat (bus 150 kV)</t>
+          <t>PLTGU Gresik</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SBRAT5</t>
+          <t>KIT_GRESIK</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>Pembangkit</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -979,11 +991,6 @@
       <c r="F8" t="inlineStr">
         <is>
           <t>150 kV</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>seksi A</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1008,12 +1015,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Gresik (bus 150 kV)</t>
+          <t>Surabaya Barat / Krian (bus 150 kV)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GRSIK5</t>
+          <t>SBRAT5</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1027,6 +1034,11 @@
       <c r="F9" t="inlineStr">
         <is>
           <t>150 kV</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>seksi A</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1051,12 +1063,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Gresik Lama</t>
+          <t>Gresik Baru (bus 150 kV)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GRLMA</t>
+          <t>GRSIK5</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1094,17 +1106,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PLTU Gresik</t>
+          <t>Gresik Lama</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>KIT_GRESIK</t>
+          <t>GRLMA</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Pembangkit</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1137,7 +1149,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kalang</t>
+          <t>Karangpilang</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1165,12 +1177,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1185,7 +1192,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Darmo</t>
+          <t>Darmo Grande</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1213,12 +1220,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>4</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1261,12 +1263,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>5;6</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1281,7 +1278,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Altap</t>
+          <t>GI ALTAP</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1372,7 +1369,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sukorejo Kreb</t>
+          <t>Sambikerep</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1400,12 +1397,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>7</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1448,12 +1440,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>18</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1496,12 +1483,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -1516,7 +1498,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Suwahan</t>
+          <t>Sawahan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1549,7 +1531,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>8;9</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -1564,7 +1546,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Pakem Mia</t>
+          <t>Petrokimia</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1592,12 +1574,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>11</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -1660,7 +1637,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Kepatihan</t>
+          <t>GI KPANG</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1746,7 +1723,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Karangbanan</t>
+          <t>Krembangan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1774,12 +1751,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>4</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -1865,12 +1837,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>18</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -1885,7 +1852,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Petrokimia</t>
+          <t>GI PTISM</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1976,7 +1943,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Gubeng</t>
+          <t>GI GBONG</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2004,12 +1971,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>12</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -2138,12 +2100,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>16</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -2158,7 +2115,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Hayam Jaya</t>
+          <t>GI HJAYA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2234,7 +2191,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>13;14</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -2249,17 +2206,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>IBT 150/70 kV Waru</t>
+          <t>GI JSTEL</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>IBT 1 WARU5</t>
+          <t>JSTEL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>IBT 3-Winding</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -2267,30 +2224,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>150/70 kV</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>WARU5</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>WARU4</t>
-        </is>
-      </c>
-      <c r="J36" t="n">
-        <v>1</v>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>IBT 150/70 kV</t>
+          <t>150 kV</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -2315,12 +2249,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Waru (bus 70 kV)</t>
+          <t>GI KSARI</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>WARU4</t>
+          <t>KSARI</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2329,11 +2263,11 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>70 kV</t>
+          <t>150 kV</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -2358,12 +2292,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Jawa Steel</t>
+          <t>Wonokromo</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>JSTEL</t>
+          <t>WKRMO</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2372,7 +2306,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2401,12 +2335,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Kesari</t>
+          <t>Ngagel</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>KSARI</t>
+          <t>NGGEL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2444,12 +2378,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Wonokromo</t>
+          <t>Kenjeran</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>WKRMO</t>
+          <t>KJRAN</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2472,7 +2406,12 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>25</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -2487,17 +2426,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Nganggel</t>
+          <t>IBT 1 Buduran 150/70 kV</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>NGGEL</t>
+          <t>IBT 1 BDRAN5</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>IBT 3-Winding</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -2505,8 +2444,26 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>150 kV</t>
-        </is>
+          <t>150/70 kV</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>BDRAN5</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>BDRAN</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>1</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
@@ -2515,12 +2472,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>17</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -2535,17 +2487,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Kejuron</t>
+          <t>IBT 7 Buduran 150/70 kV</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>KJRAN</t>
+          <t>IBT 7 BDRAN5</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>IBT 3-Winding</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -2553,8 +2505,26 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>150 kV</t>
-        </is>
+          <t>150/70 kV</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>BDRAN5</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>BDRAN</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>1</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
@@ -2578,17 +2548,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>IBT 1 Buduran 150/70 kV</t>
+          <t>Buduran (bus 70 kV)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>IBT 1 BDRAN5</t>
+          <t>BDRAN</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>IBT 3-Winding</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -2596,26 +2566,8 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>150/70 kV</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>BDRAN5</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>BDRAN</t>
-        </is>
-      </c>
-      <c r="J43" t="n">
-        <v>1</v>
+          <t>70 kV</t>
+        </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
@@ -2624,12 +2576,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>13</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -2644,17 +2591,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>IBT 7 Buduran 150/70 kV</t>
+          <t>New Buduran</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>IBT 7 BDRAN5</t>
+          <t>NBRAN5</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>IBT 3-Winding</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -2662,26 +2609,8 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>150/70 kV</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>BDRAN5</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>BDRAN</t>
-        </is>
-      </c>
-      <c r="J44" t="n">
-        <v>1</v>
+          <t>150 kV</t>
+        </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
@@ -2690,12 +2619,7 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>13</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -2710,12 +2634,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Buduran (bus 70 kV)</t>
+          <t>Simpang</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>BDRAN</t>
+          <t>SIMPG</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2724,11 +2648,11 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>70 kV</t>
+          <t>150 kV</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -2753,12 +2677,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>New Buduran</t>
+          <t>Sidoarjo</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>NBRAN5</t>
+          <t>SDRJO</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2767,7 +2691,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -2796,12 +2720,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Simpang</t>
+          <t>Sedati</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SIMPG</t>
+          <t>SDATI</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2839,12 +2763,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Sidoarjo</t>
+          <t>Maspion</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>SDRJO</t>
+          <t>MPION</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2857,7 +2781,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>150 kV</t>
+          <t>70 kV</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -2867,7 +2791,12 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>15</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -2882,12 +2811,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Sedati</t>
+          <t>Kedinding</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SDATI</t>
+          <t>KDING</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2900,7 +2829,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>70 kV</t>
+          <t>150 kV</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -2925,12 +2854,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Mpion</t>
+          <t>Gilitimur</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MPION</t>
+          <t>GLMUR</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2939,11 +2868,11 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>70 kV</t>
+          <t>150 kV</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -2953,12 +2882,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>15</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -2973,12 +2897,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Kedinding</t>
+          <t>Bangkalan</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>KDING</t>
+          <t>BKLAN</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2987,13 +2911,18 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
           <t>150 kV</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>seksi A/B</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr">
         <is>
           <t>Beroperasi</t>
@@ -3006,7 +2935,7 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>22;23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -3021,12 +2950,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Gelam Ur</t>
+          <t>Sampang</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>GLMUR</t>
+          <t>SAMPG</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3035,7 +2964,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -3049,12 +2978,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -3069,12 +2993,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Bangkalan</t>
+          <t>Pamekasan</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>BKLAN</t>
+          <t>PKSAN</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3083,18 +3007,13 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
           <t>150 kV</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>seksi A/B</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr">
         <is>
           <t>Beroperasi</t>
@@ -3102,12 +3021,7 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>21;22</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -3122,12 +3036,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Sampang</t>
+          <t>Guluk-Guluk</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>SAMPG</t>
+          <t>GULUK</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3136,7 +3050,7 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -3155,7 +3069,7 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -3170,12 +3084,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Pamekasan</t>
+          <t>Sumenep</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>PKSAN</t>
+          <t>SMNEP</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3184,7 +3098,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -3198,106 +3112,10 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>24</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
-        <is>
-          <t>Jawa Timur</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>55</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Guluk-Guluk</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>GULUK</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Busbar GI</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>11</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="R56" t="inlineStr">
-        <is>
-          <t>Jawa Timur</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>56</v>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Sumenep</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>SMNEP</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Busbar GI</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>12</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="R57" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
@@ -3314,7 +3132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q46"/>
+  <dimension ref="A1:Q55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3410,7 +3228,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Outlet PLTU Gresik</t>
+          <t>Outlet PLTGU Gresik</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -3462,19 +3280,24 @@
       <c r="A3" t="n">
         <v>2</v>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SUTT Gresik - Gresik Lama</t>
+          <t>SKTT Surabaya Barat - Karangpilang</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>GRSIK5</t>
+          <t>SBRAT5</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>GRLMA</t>
+          <t>KLANG</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -3492,7 +3315,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Sangat Rawan</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -3504,7 +3327,7 @@
         <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -3516,24 +3339,19 @@
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SUTT Surabaya Barat - Kalang</t>
+          <t>SUTT Karangpilang - Bambe</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SBRAT5</t>
+          <t>KLANG</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>KLANG</t>
+          <t>BAMBE</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -3551,7 +3369,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Sangat Rawan</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -3560,10 +3378,10 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -3582,7 +3400,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SUTT Surabaya Barat - Darmo</t>
+          <t>SUTT Surabaya Barat - Sawahan</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -3592,7 +3410,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>DARMO</t>
+          <t>SWHAN</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -3622,7 +3440,7 @@
         <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -3641,7 +3459,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SUTT Surabaya Barat - Tandes</t>
+          <t>SUTT Surabaya Barat - Darmo Grande</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -3651,7 +3469,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>TNDES</t>
+          <t>DARMO</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -3695,22 +3513,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SUTT Kalang - Bambe</t>
+          <t>SUTT Darmo Grande - Waru</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>KLANG</t>
+          <t>DARMO</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>BAMBE</t>
+          <t>WARU5</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -3740,7 +3558,7 @@
         <v>2</v>
       </c>
       <c r="O7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -3752,24 +3570,19 @@
       <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SUTT Darmo - Suwahan</t>
+          <t>SUTT Surabaya Barat - ALTAP</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>DARMO</t>
+          <t>SBRAT5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SWHAN</t>
+          <t>ALTAP</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -3787,7 +3600,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Sangat Rawan</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3796,10 +3609,10 @@
         </is>
       </c>
       <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="n">
         <v>2</v>
-      </c>
-      <c r="O8" t="n">
-        <v>3</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -3813,22 +3626,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SUTT Tandes - Suwahan</t>
+          <t>SUTT Gresik Baru - Tandes</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>GRSIK5</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>TNDES</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>SWHAN</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -3855,10 +3668,10 @@
         </is>
       </c>
       <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
         <v>2</v>
-      </c>
-      <c r="O9" t="n">
-        <v>3</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -3872,17 +3685,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SUTT Bambe - Kepatihan</t>
+          <t>SUTT Gresik Lama - ALTAP</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>BAMBE</t>
+          <t>GRLMA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>KPANG</t>
+          <t>ALTAP</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -3909,10 +3722,10 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -3926,17 +3739,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SUTT Bambe - Undaan</t>
+          <t>SUTT ALTAP - Segoromadu</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>BAMBE</t>
+          <t>ALTAP</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>UDAAN</t>
+          <t>SGMDU</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -3963,10 +3776,10 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -3978,24 +3791,19 @@
       <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SUTT Suwahan - Karangbanan</t>
+          <t>SUTT Gresik Lama - Segoromadu</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SWHAN</t>
+          <t>GRLMA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>KRBAN</t>
+          <t>SGMDU</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -4013,7 +3821,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Sangat Rawan</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -4022,10 +3830,10 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
@@ -4039,17 +3847,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SUTT Tandes - Gunungsari</t>
+          <t>SUTT Segoromadu - Petrokimia</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>TNDES</t>
+          <t>SGMDU</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>GNSRI</t>
+          <t>PKMIA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -4079,7 +3887,7 @@
         <v>2</v>
       </c>
       <c r="O13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
@@ -4091,19 +3899,24 @@
       <c r="A14" t="n">
         <v>13</v>
       </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SUTT Kepatihan - Rungkut</t>
+          <t>SUTT Gresik Lama - Sambikerep</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>KPANG</t>
+          <t>GRLMA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RNKUT</t>
+          <t>SKREP</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -4121,7 +3934,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Sangat Rawan</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -4130,10 +3943,10 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -4147,22 +3960,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SUTT Karangbanan - Gubeng</t>
+          <t>SUTT Sambikerep - Waru</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>KRBAN</t>
+          <t>SKREP</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>GBONG</t>
+          <t>WARU5</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -4189,7 +4002,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O15" t="n">
         <v>5</v>
@@ -4206,17 +4019,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SUTT Kalang - Surabaya Selatan</t>
+          <t>SUTT Gresik Lama - Wilmar</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>KLANG</t>
+          <t>GRLMA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SBSEL</t>
+          <t>WLMAR</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -4225,28 +4038,28 @@
         </is>
       </c>
       <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Jawa Timur</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
         <v>2</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>Jawa Timur</t>
-        </is>
-      </c>
-      <c r="N16" t="n">
-        <v>2</v>
-      </c>
-      <c r="O16" t="n">
-        <v>6</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -4260,22 +4073,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SUTT Rungkut - Sukolilo</t>
+          <t>SUTT Tandes - Sawahan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>RNKUT</t>
+          <t>TNDES</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SLILO</t>
+          <t>SWHAN</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -4302,10 +4115,10 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O17" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
@@ -4317,19 +4130,24 @@
       <c r="A18" t="n">
         <v>17</v>
       </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SUTT Gubeng - Hayam Jaya</t>
+          <t>SUTT Sawahan - Gunungsari</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>GBONG</t>
+          <t>SWHAN</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>HJAYA</t>
+          <t>GNSRI</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -4347,7 +4165,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Sangat Rawan</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -4356,10 +4174,10 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O18" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
@@ -4371,19 +4189,24 @@
       <c r="A19" t="n">
         <v>18</v>
       </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SUTT Surabaya Selatan - Kesari</t>
+          <t>SUTT Gunungsari - Waru</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SBSEL</t>
+          <t>GNSRI</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>KSARI</t>
+          <t>WARU5</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4401,7 +4224,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Sangat Rawan</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -4410,10 +4233,10 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
@@ -4425,19 +4248,24 @@
       <c r="A20" t="n">
         <v>19</v>
       </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SUTT Sukolilo - Wonokromo</t>
+          <t>SUTT Tandes - Perak</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SLILO</t>
+          <t>TNDES</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>WKRMO</t>
+          <t>PERAK</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4446,28 +4274,28 @@
         </is>
       </c>
       <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Sangat Rawan</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Jawa Timur</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
         <v>2</v>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>Jawa Timur</t>
-        </is>
-      </c>
-      <c r="N20" t="n">
-        <v>6</v>
-      </c>
       <c r="O20" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
@@ -4481,22 +4309,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SUTT Hayam Jaya - Nganggel</t>
+          <t>SUTT Perak - Ujung</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>HJAYA</t>
+          <t>PERAK</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>NGGEL</t>
+          <t>UJUNG</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4505,7 +4333,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -4523,10 +4351,10 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O21" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
@@ -4538,19 +4366,24 @@
       <c r="A22" t="n">
         <v>21</v>
       </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SUTT Hayam Jaya - Kejuron</t>
+          <t>SUTT Tandes - Ujung</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>HJAYA</t>
+          <t>TNDES</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>KJRAN</t>
+          <t>UJUNG</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4559,28 +4392,28 @@
         </is>
       </c>
       <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Sangat Rawan</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Jawa Timur</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
         <v>2</v>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>Jawa Timur</t>
-        </is>
-      </c>
-      <c r="N22" t="n">
-        <v>6</v>
-      </c>
       <c r="O22" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
@@ -4594,17 +4427,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SUTT Nganggel - Simpang</t>
+          <t>SKTT Perak - PTISM</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NGGEL</t>
+          <t>PERAK</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>SIMPG</t>
+          <t>PTISM</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4613,7 +4446,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -4631,10 +4464,10 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O23" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
@@ -4648,22 +4481,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SUTT Kejuron - Gelam Ur</t>
+          <t>SUTT Karangpilang - Rungkut</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>KJRAN</t>
+          <t>KLANG</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>GLMUR</t>
+          <t>RNKUT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4690,10 +4523,10 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O24" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
@@ -4707,17 +4540,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SUTT Gresik Lama - Altap</t>
+          <t>SUTT Bambe - KPANG</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>GRLMA</t>
+          <t>BAMBE</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ALTAP</t>
+          <t>KPANG</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -4744,10 +4577,10 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
@@ -4761,17 +4594,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SUTT Gresik Lama - Segoromadu</t>
+          <t>SKTT Sawahan - Undaan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>GRLMA</t>
+          <t>SWHAN</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>SGMDU</t>
+          <t>UDAAN</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -4798,10 +4631,10 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
@@ -4813,24 +4646,19 @@
       <c r="A27" t="n">
         <v>26</v>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SUTT Gresik Lama - Sukorejo Kreb</t>
+          <t>SKTT Undaan - GBONG</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>GRLMA</t>
+          <t>UDAAN</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SKREP</t>
+          <t>GBONG</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -4848,7 +4676,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Sangat Rawan</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -4857,10 +4685,10 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O27" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
@@ -4872,24 +4700,19 @@
       <c r="A28" t="n">
         <v>27</v>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SUTT Gresik Lama - Wilmar</t>
+          <t>SKTT Sawahan - Krembangan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>GRLMA</t>
+          <t>SWHAN</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>WLMAR</t>
+          <t>KRBAN</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -4907,7 +4730,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Sangat Rawan</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -4916,10 +4739,10 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
@@ -4933,22 +4756,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SUTT Segoromadu - Pakem Mia</t>
+          <t>SUTT Waru - Rungkut</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SGMDU</t>
+          <t>WARU5</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>PKMIA</t>
+          <t>RNKUT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -4975,10 +4798,10 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
@@ -4992,22 +4815,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SUTT Wilmar - Perak</t>
+          <t>SUTT Rungkut - Sukolilo</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>WLMAR</t>
+          <t>RNKUT</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>PERAK</t>
+          <t>SLILO</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -5034,10 +4857,10 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O30" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
@@ -5049,24 +4872,19 @@
       <c r="A31" t="n">
         <v>30</v>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SUTT Wilmar - Ujung</t>
+          <t>SUTT Rungkut - Surabaya Selatan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>WLMAR</t>
+          <t>RNKUT</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>UJUNG</t>
+          <t>SBSEL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -5084,7 +4902,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Sangat Rawan</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -5093,10 +4911,10 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O31" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
@@ -5110,17 +4928,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SUTT Perak - Petrokimia</t>
+          <t>SUTT Surabaya Selatan - KSARI</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>PERAK</t>
+          <t>SBSEL</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>PTISM</t>
+          <t>KSARI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -5147,10 +4965,10 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O32" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
@@ -5164,17 +4982,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SUTT Sukorejo Kreb - Waru</t>
+          <t>SKTT Rungkut - HJAYA</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>SKREP</t>
+          <t>RNKUT</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>WARU5</t>
+          <t>HJAYA</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -5183,7 +5001,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -5201,10 +5019,10 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
@@ -5218,17 +5036,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SUTT Gunungsari - Waru</t>
+          <t>SKTT Sukolilo - KSARI</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>GNSRI</t>
+          <t>SLILO</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>WARU5</t>
+          <t>KSARI</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -5255,10 +5073,10 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O34" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
@@ -5270,24 +5088,19 @@
       <c r="A35" t="n">
         <v>34</v>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SUTT Waru - Buduran</t>
+          <t>SUTT Sukolilo - Wonokromo</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>WARU5</t>
+          <t>SLILO</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>BDRAN5</t>
+          <t>WKRMO</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -5305,7 +5118,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Sangat Rawan</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -5314,10 +5127,10 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O35" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
@@ -5329,24 +5142,19 @@
       <c r="A36" t="n">
         <v>35</v>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SUTT Waru - Jawa Steel</t>
+          <t>SKTT Sukolilo - Ngagel</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>WARU5</t>
+          <t>SLILO</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>JSTEL</t>
+          <t>NGGEL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -5364,7 +5172,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Sangat Rawan</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -5373,10 +5181,10 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O36" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
@@ -5390,17 +5198,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>SUTT Buduran - New Buduran</t>
+          <t>SUTT Ngagel - Simpang</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>BDRAN5</t>
+          <t>NGGEL</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>NBRAN5</t>
+          <t>SIMPG</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -5427,10 +5235,10 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O37" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
@@ -5442,19 +5250,24 @@
       <c r="A38" t="n">
         <v>37</v>
       </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SUTT New Buduran - Sidoarjo</t>
+          <t>SUTT Sukolilo - Kenjeran</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NBRAN5</t>
+          <t>SLILO</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>SDRJO</t>
+          <t>KJRAN</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -5472,7 +5285,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Sangat Rawan</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -5481,10 +5294,10 @@
         </is>
       </c>
       <c r="N38" t="n">
+        <v>6</v>
+      </c>
+      <c r="O38" t="n">
         <v>7</v>
-      </c>
-      <c r="O38" t="n">
-        <v>8</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
@@ -5496,28 +5309,33 @@
       <c r="A39" t="n">
         <v>38</v>
       </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SUTT 70 kV Buduran - Sedati</t>
+          <t>SUTT Waru - Sidoarjo</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>BDRAN</t>
+          <t>WARU5</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>SDATI</t>
+          <t>SDRJO</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>70 kV</t>
+          <t>150 kV</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -5526,7 +5344,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Sangat Rawan</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -5535,7 +5353,7 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O39" t="n">
         <v>8</v>
@@ -5552,31 +5370,31 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SUTT 70 kV Buduran - Mpion</t>
+          <t>SUTT Waru - Buduran</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>BDRAN</t>
+          <t>WARU5</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>MPION</t>
+          <t>BDRAN5</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>70 kV</t>
+          <t>150 kV</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -5594,10 +5412,10 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O40" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
@@ -5611,22 +5429,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>SUTT Ujung - Kedinding</t>
+          <t>SUTT Buduran - New Buduran</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>UJUNG</t>
+          <t>BDRAN5</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>KDING</t>
+          <t>NBRAN5</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -5635,7 +5453,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -5653,10 +5471,10 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O41" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
@@ -5668,24 +5486,19 @@
       <c r="A42" t="n">
         <v>41</v>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>21;22</t>
-        </is>
-      </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SUTT Kedinding - Bangkalan</t>
+          <t>SUTT New Buduran - Sidoarjo</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>KDING</t>
+          <t>NBRAN5</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>BKLAN</t>
+          <t>SDRJO</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -5694,7 +5507,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -5703,7 +5516,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Sangat Rawan</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -5712,10 +5525,10 @@
         </is>
       </c>
       <c r="N42" t="n">
+        <v>7</v>
+      </c>
+      <c r="O42" t="n">
         <v>8</v>
-      </c>
-      <c r="O42" t="n">
-        <v>9</v>
       </c>
       <c r="P42" t="inlineStr">
         <is>
@@ -5727,24 +5540,19 @@
       <c r="A43" t="n">
         <v>42</v>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SUTT Bangkalan - Sampang</t>
+          <t>SUTT New Buduran - Sedati</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>BKLAN</t>
+          <t>NBRAN5</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>SAMPG</t>
+          <t>SDATI</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -5762,7 +5570,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Sangat Rawan</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -5771,10 +5579,10 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O43" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
@@ -5786,24 +5594,19 @@
       <c r="A44" t="n">
         <v>43</v>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SUTT Sampang - Pamekasan</t>
+          <t>SUTT Waru - JSTEL</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>SAMPG</t>
+          <t>WARU5</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>PKSAN</t>
+          <t>JSTEL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -5812,7 +5615,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -5821,7 +5624,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Sangat Rawan</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -5830,10 +5633,10 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="O44" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="P44" t="inlineStr">
         <is>
@@ -5845,29 +5648,24 @@
       <c r="A45" t="n">
         <v>44</v>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>SUTT Pamekasan - Guluk-Guluk</t>
+          <t>SUTT 70 kV Buduran - Maspion</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>PKSAN</t>
+          <t>BDRAN</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>GULUK</t>
+          <t>MPION</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>150 kV</t>
+          <t>70 kV</t>
         </is>
       </c>
       <c r="H45" t="n">
@@ -5880,7 +5678,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Sangat Rawan</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -5889,10 +5687,10 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="O45" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="P45" t="inlineStr">
         <is>
@@ -5904,51 +5702,577 @@
       <c r="A46" t="n">
         <v>45</v>
       </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
       <c r="C46" t="inlineStr">
         <is>
+          <t>SUTT Ujung - Kedinding</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>UJUNG</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>KDING</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Sangat Rawan</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Jawa Timur</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>4</v>
+      </c>
+      <c r="O46" t="n">
+        <v>8</v>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Tidak</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>SUTT Ujung - Bangkalan</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>UJUNG</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>BKLAN</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Sangat Rawan</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Jawa Timur</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>4</v>
+      </c>
+      <c r="O47" t="n">
+        <v>9</v>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Tidak</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>SUTT Kedinding - Bangkalan</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>KDING</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>BKLAN</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>2</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Sangat Rawan</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Jawa Timur</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>8</v>
+      </c>
+      <c r="O48" t="n">
+        <v>9</v>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Tidak</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>SUTT Kenjeran - Kedinding</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>KJRAN</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>KDING</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Sangat Rawan</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Jawa Timur</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>7</v>
+      </c>
+      <c r="O49" t="n">
+        <v>8</v>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Tidak</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>SUTT Kenjeran - Gilitimur</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>KJRAN</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>GLMUR</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>1</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Sangat Rawan</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Jawa Timur</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>7</v>
+      </c>
+      <c r="O50" t="n">
+        <v>9</v>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Tidak</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>SUTT Gilitimur - Bangkalan</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>GLMUR</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>BKLAN</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Sangat Rawan</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Jawa Timur</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>9</v>
+      </c>
+      <c r="O51" t="n">
+        <v>9</v>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Tidak</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>SUTT Bangkalan - Sampang</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>BKLAN</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>SAMPG</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>2</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Sangat Rawan</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Jawa Timur</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>9</v>
+      </c>
+      <c r="O52" t="n">
+        <v>10</v>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Tidak</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>SUTT Sampang - Pamekasan</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>SAMPG</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>PKSAN</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>2</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Sangat Rawan</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Jawa Timur</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>10</v>
+      </c>
+      <c r="O53" t="n">
+        <v>11</v>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Tidak</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>SUTT Pamekasan - Guluk-Guluk</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>PKSAN</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>GULUK</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>2</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Jawa Timur</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>11</v>
+      </c>
+      <c r="O54" t="n">
+        <v>12</v>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Tidak</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
           <t>SUTT Guluk-Guluk - Sumenep</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>GULUK</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>SMNEP</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="H46" t="n">
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
         <v>2</v>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>Jawa Timur</t>
-        </is>
-      </c>
-      <c r="N46" t="n">
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Jawa Timur</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
         <v>12</v>
       </c>
-      <c r="O46" t="n">
+      <c r="O55" t="n">
         <v>13</v>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="P55" t="inlineStr">
         <is>
           <t>Tidak</t>
         </is>

--- a/samples/ss_krian12_gresik_ingest.xlsx
+++ b/samples/ss_krian12_gresik_ingest.xlsx
@@ -10,7 +10,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gardu_Induk_dan_Aset" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jalur_Transmisi" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Kerawanan_Detail" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kopel_Bus" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Kerawanan_Detail" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -506,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U55"/>
+  <dimension ref="A1:X55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -615,6 +616,21 @@
           <t>Longitude</t>
         </is>
       </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Seksi Bus</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Seksi Bus HV</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Seksi Bus LV</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -1519,6 +1535,11 @@
           <t>150 kV</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Seksi 1/2: ID model; bay belum dipetakan; kopel OPEN per risiko #9</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr">
         <is>
           <t>Beroperasi</t>
@@ -1537,6 +1558,11 @@
       <c r="R20" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>1;2</t>
         </is>
       </c>
     </row>
@@ -1936,6 +1962,11 @@
           <t>Jawa Timur</t>
         </is>
       </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>A;B</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2941,6 +2972,11 @@
       <c r="R51" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>A;B</t>
         </is>
       </c>
     </row>
@@ -3132,7 +3168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q55"/>
+  <dimension ref="A1:T56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3221,6 +3257,21 @@
           <t>Sudut Pandang</t>
         </is>
       </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Seksi Dari</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Seksi Ke</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>No Sirkit</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -4299,7 +4350,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Tidak</t>
+          <t>Ya</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4409,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Tidak</t>
+          <t>Ya</t>
         </is>
       </c>
     </row>
@@ -4533,6 +4584,11 @@
           <t>Tidak</t>
         </is>
       </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -4808,6 +4864,11 @@
           <t>Tidak</t>
         </is>
       </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4867,6 +4928,11 @@
           <t>Tidak</t>
         </is>
       </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4921,6 +4987,11 @@
           <t>Tidak</t>
         </is>
       </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -5029,6 +5100,11 @@
           <t>Tidak</t>
         </is>
       </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -5815,6 +5891,11 @@
           <t>Tidak</t>
         </is>
       </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5874,6 +5955,11 @@
           <t>Tidak</t>
         </is>
       </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5989,7 +6075,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Tidak</t>
+          <t>Ya</t>
         </is>
       </c>
     </row>
@@ -6048,7 +6134,12 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Tidak</t>
+          <t>Ya</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -6082,7 +6173,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -6108,6 +6199,16 @@
       <c r="P52" t="inlineStr">
         <is>
           <t>Tidak</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -6117,31 +6218,31 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>SUTT Sampang - Pamekasan</t>
+          <t>SUTT Bangkalan - Sampang</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
+          <t>BKLAN</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
           <t>SAMPG</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>PKSAN</t>
-        </is>
-      </c>
       <c r="F53" t="inlineStr">
         <is>
           <t>150 kV</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -6159,14 +6260,24 @@
         </is>
       </c>
       <c r="N53" t="n">
+        <v>9</v>
+      </c>
+      <c r="O53" t="n">
         <v>10</v>
       </c>
-      <c r="O53" t="n">
-        <v>11</v>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Tidak</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -6174,19 +6285,24 @@
       <c r="A54" t="n">
         <v>53</v>
       </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>SUTT Pamekasan - Guluk-Guluk</t>
+          <t>SUTT Sampang - Pamekasan</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
+          <t>SAMPG</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
           <t>PKSAN</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>GULUK</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -6204,7 +6320,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Sangat Rawan</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -6213,10 +6329,10 @@
         </is>
       </c>
       <c r="N54" t="n">
+        <v>10</v>
+      </c>
+      <c r="O54" t="n">
         <v>11</v>
-      </c>
-      <c r="O54" t="n">
-        <v>12</v>
       </c>
       <c r="P54" t="inlineStr">
         <is>
@@ -6230,17 +6346,17 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>SUTT Guluk-Guluk - Sumenep</t>
+          <t>SUTT Pamekasan - Guluk-Guluk</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
+          <t>PKSAN</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
           <t>GULUK</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>SMNEP</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -6267,12 +6383,66 @@
         </is>
       </c>
       <c r="N55" t="n">
+        <v>11</v>
+      </c>
+      <c r="O55" t="n">
         <v>12</v>
       </c>
-      <c r="O55" t="n">
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Tidak</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>SUTT Guluk-Guluk - Sumenep</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>GULUK</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>SMNEP</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>2</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Jawa Timur</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>12</v>
+      </c>
+      <c r="O56" t="n">
         <v>13</v>
       </c>
-      <c r="P55" t="inlineStr">
+      <c r="P56" t="inlineStr">
         <is>
           <t>Tidak</t>
         </is>
@@ -6289,6 +6459,168 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Kode GI</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ID Kopel</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Seksi Dari</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Seksi Ke</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Status Kopel</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>No Kerawanan</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Catatan</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Sudut Pandang</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>RNKUT</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>KOP_AB</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Kopel Rungkut A-B; Gambar 5.3; splitting sesuai mitigasi #3. Posisi sumber buku, bukan telemetri.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BKLAN</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>KOP_AB</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Kopel Bangkalan A-B dibuka; Tabel 5.1 #21 dan Gambar 5.3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SWHAN</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>KOP_12</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Kopel Sawahan dibuka per #9; terminal belum dipetakan; 1/2 adalah ID model.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
